--- a/artfynd/A 63663-2025 artfynd.xlsx
+++ b/artfynd/A 63663-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112056985</v>
+        <v>112056771</v>
       </c>
       <c r="B2" t="n">
-        <v>90815</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471107</v>
+        <v>471058</v>
       </c>
       <c r="R2" t="n">
-        <v>6878973</v>
+        <v>6878706</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -778,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112056968</v>
+        <v>112056821</v>
       </c>
       <c r="B3" t="n">
-        <v>90809</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -794,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471056</v>
+        <v>471005</v>
       </c>
       <c r="R3" t="n">
-        <v>6878932</v>
+        <v>6878689</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -881,15 +871,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112057042</v>
+        <v>112106065</v>
       </c>
       <c r="B4" t="n">
-        <v>90809</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,35 +882,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Byn, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471107</v>
+        <v>470881</v>
       </c>
       <c r="R4" t="n">
-        <v>6878973</v>
+        <v>6879329</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -952,12 +937,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,15 +969,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112056821</v>
+        <v>119483639</v>
       </c>
       <c r="B5" t="n">
-        <v>90807</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,18 +997,26 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Byn, Hjd</t>
+          <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471005</v>
+        <v>471001</v>
       </c>
       <c r="R5" t="n">
-        <v>6878690</v>
+        <v>6878779</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1055,12 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,15 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112106066</v>
+        <v>119483766</v>
       </c>
       <c r="B6" t="n">
-        <v>90847</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,35 +1086,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>470882</v>
+        <v>471006</v>
       </c>
       <c r="R6" t="n">
-        <v>6879329</v>
+        <v>6878778</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1158,12 +1149,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,15 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112106172</v>
+        <v>119722350</v>
       </c>
       <c r="B7" t="n">
-        <v>90847</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,38 +1192,44 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>470975</v>
+        <v>471026</v>
       </c>
       <c r="R7" t="n">
-        <v>6879312</v>
+        <v>6878688</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1261,12 +1253,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,27 +1283,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112106065</v>
+        <v>119722627</v>
       </c>
       <c r="B8" t="n">
-        <v>90845</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1326,21 +1323,31 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470882</v>
+        <v>470974</v>
       </c>
       <c r="R8" t="n">
-        <v>6879329</v>
+        <v>6878769</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1364,12 +1371,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1384,27 +1401,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119483848</v>
+        <v>119723069</v>
       </c>
       <c r="B9" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1412,46 +1424,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Byn, Byn, Hjd</t>
+          <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470976</v>
+        <v>471053</v>
       </c>
       <c r="R9" t="n">
-        <v>6878820</v>
+        <v>6878751</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1475,12 +1489,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1495,27 +1519,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119483537</v>
+        <v>119851125</v>
       </c>
       <c r="B10" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,43 +1542,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Byn, Byn, Hjd</t>
+          <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471054</v>
+        <v>470895</v>
       </c>
       <c r="R10" t="n">
-        <v>6878750</v>
+        <v>6878676</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1586,12 +1603,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1606,65 +1633,71 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119483868</v>
+        <v>119851206</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Byn, Byn, Hjd</t>
+          <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470973</v>
+        <v>470886</v>
       </c>
       <c r="R11" t="n">
-        <v>6878820</v>
+        <v>6878669</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1688,12 +1721,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1708,65 +1751,67 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119483661</v>
+        <v>119851909</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Byn, Byn, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471001</v>
+        <v>470853</v>
       </c>
       <c r="R12" t="n">
-        <v>6878779</v>
+        <v>6878846</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1790,12 +1835,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1810,27 +1865,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119484942</v>
+        <v>119852400</v>
       </c>
       <c r="B13" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,46 +1888,44 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Byn, Byn, Hjd</t>
+          <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471057</v>
+        <v>471011</v>
       </c>
       <c r="R13" t="n">
-        <v>6878837</v>
+        <v>6878716</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1901,12 +1949,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1921,71 +1979,58 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119483742</v>
+        <v>112056968</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Byn, Byn, Hjd</t>
+          <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471010</v>
+        <v>471057</v>
       </c>
       <c r="R14" t="n">
-        <v>6878760</v>
+        <v>6878932</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2012,12 +2057,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2044,15 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119483969</v>
+        <v>112057042</v>
       </c>
       <c r="B15" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,26 +2117,18 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Byn, Byn, Hjd</t>
+          <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471041</v>
+        <v>471107</v>
       </c>
       <c r="R15" t="n">
-        <v>6878936</v>
+        <v>6878973</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2123,12 +2155,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2155,15 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119483639</v>
+        <v>112105915</v>
       </c>
       <c r="B16" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2171,43 +2198,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Byn, Byn, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471001</v>
+        <v>470952</v>
       </c>
       <c r="R16" t="n">
-        <v>6878779</v>
+        <v>6879263</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2234,12 +2253,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2266,15 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119483785</v>
+        <v>112106066</v>
       </c>
       <c r="B17" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,26 +2313,18 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Byn, Byn, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470997</v>
+        <v>470881</v>
       </c>
       <c r="R17" t="n">
-        <v>6878764</v>
+        <v>6879329</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2345,12 +2351,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,15 +2383,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119484702</v>
+        <v>112106172</v>
       </c>
       <c r="B18" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2410,26 +2411,18 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Byn, Byn, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471098</v>
+        <v>470975</v>
       </c>
       <c r="R18" t="n">
-        <v>6878877</v>
+        <v>6879312</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2456,12 +2449,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2488,50 +2481,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119484128</v>
+        <v>119483537</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471106</v>
+        <v>471054</v>
       </c>
       <c r="R19" t="n">
-        <v>6878960</v>
+        <v>6878750</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2590,15 +2587,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119483937</v>
+        <v>119483707</v>
       </c>
       <c r="B20" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2639,13 +2631,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>470993</v>
+        <v>471012</v>
       </c>
       <c r="R20" t="n">
-        <v>6878920</v>
+        <v>6878782</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2701,15 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119483707</v>
+        <v>119483785</v>
       </c>
       <c r="B21" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2741,7 +2728,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2750,13 +2737,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471012</v>
+        <v>470997</v>
       </c>
       <c r="R21" t="n">
-        <v>6878782</v>
+        <v>6878764</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2812,15 +2799,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119483766</v>
+        <v>119483848</v>
       </c>
       <c r="B22" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2828,21 +2810,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2861,10 +2843,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471006</v>
+        <v>470976</v>
       </c>
       <c r="R22" t="n">
-        <v>6878778</v>
+        <v>6878820</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2923,15 +2905,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119484119</v>
+        <v>119483937</v>
       </c>
       <c r="B23" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,7 +2940,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2972,10 +2949,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471106</v>
+        <v>470993</v>
       </c>
       <c r="R23" t="n">
-        <v>6878960</v>
+        <v>6878920</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3034,50 +3011,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119484855</v>
+        <v>119483969</v>
       </c>
       <c r="B24" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>471057</v>
+        <v>471041</v>
       </c>
       <c r="R24" t="n">
-        <v>6878837</v>
+        <v>6878936</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3136,37 +3117,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119724366</v>
+        <v>119484119</v>
       </c>
       <c r="B25" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3176,24 +3152,22 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>471081</v>
+        <v>471106</v>
       </c>
       <c r="R25" t="n">
-        <v>6878832</v>
+        <v>6878960</v>
       </c>
       <c r="S25" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3217,22 +3191,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:37</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:37</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3247,54 +3211,49 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119724502</v>
+        <v>119484702</v>
       </c>
       <c r="B26" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3302,21 +3261,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>470964</v>
+        <v>471098</v>
       </c>
       <c r="R26" t="n">
-        <v>6878819</v>
+        <v>6878877</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3340,22 +3297,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3370,49 +3317,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119723116</v>
+        <v>119484942</v>
       </c>
       <c r="B27" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3422,24 +3364,22 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Byn, Hjd</t>
+          <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471051</v>
+        <v>471057</v>
       </c>
       <c r="R27" t="n">
-        <v>6878742</v>
+        <v>6878837</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3463,22 +3403,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3493,27 +3423,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119723069</v>
+        <v>119722408</v>
       </c>
       <c r="B28" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3521,26 +3446,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3556,13 +3481,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471053</v>
+        <v>470980</v>
       </c>
       <c r="R28" t="n">
-        <v>6878751</v>
+        <v>6878652</v>
       </c>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3591,7 +3516,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3601,7 +3526,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3628,42 +3553,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119724435</v>
+        <v>119722501</v>
       </c>
       <c r="B29" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3675,17 +3595,17 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>471045</v>
+        <v>470963</v>
       </c>
       <c r="R29" t="n">
-        <v>6878839</v>
+        <v>6878709</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3714,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3724,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3751,15 +3671,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119722627</v>
+        <v>119722838</v>
       </c>
       <c r="B30" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3767,26 +3682,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3798,17 +3713,17 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Byn, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>470974</v>
+        <v>471024</v>
       </c>
       <c r="R30" t="n">
-        <v>6878769</v>
+        <v>6878826</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3837,7 +3752,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3847,7 +3762,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3877,12 +3792,7 @@
         <v>119722968</v>
       </c>
       <c r="B31" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3997,15 +3907,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119722501</v>
+        <v>119851314</v>
       </c>
       <c r="B32" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4032,7 +3937,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4048,13 +3953,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>470963</v>
+        <v>470863</v>
       </c>
       <c r="R32" t="n">
-        <v>6878709</v>
+        <v>6878623</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4078,22 +3983,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4120,15 +4025,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119722838</v>
+        <v>119852126</v>
       </c>
       <c r="B33" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,7 +4055,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4171,13 +4071,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471024</v>
+        <v>471009</v>
       </c>
       <c r="R33" t="n">
-        <v>6878826</v>
+        <v>6878908</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4201,22 +4101,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4243,49 +4143,36 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119724643</v>
+        <v>119852152</v>
       </c>
       <c r="B34" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -4294,10 +4181,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>470980</v>
+        <v>471012</v>
       </c>
       <c r="R34" t="n">
-        <v>6878815</v>
+        <v>6878913</v>
       </c>
       <c r="S34" t="n">
         <v>7</v>
@@ -4324,22 +4211,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4366,15 +4253,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119722350</v>
+        <v>119852187</v>
       </c>
       <c r="B35" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4382,44 +4264,48 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Byn, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471026</v>
+        <v>471061</v>
       </c>
       <c r="R35" t="n">
-        <v>6878688</v>
+        <v>6878956</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4443,22 +4329,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4485,15 +4371,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119722408</v>
+        <v>119852292</v>
       </c>
       <c r="B36" t="n">
-        <v>92024</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4518,11 +4399,7 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -4532,17 +4409,17 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Byn, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>470980</v>
+        <v>471113</v>
       </c>
       <c r="R36" t="n">
-        <v>6878652</v>
+        <v>6878966</v>
       </c>
       <c r="S36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4566,22 +4443,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4608,19 +4485,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119724688</v>
+        <v>112056985</v>
       </c>
       <c r="B37" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4641,31 +4513,21 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>471003</v>
+        <v>471107</v>
       </c>
       <c r="R37" t="n">
-        <v>6878824</v>
+        <v>6878973</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4689,22 +4551,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:55</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:55</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4719,27 +4571,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119851069</v>
+        <v>119483661</v>
       </c>
       <c r="B38" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4747,48 +4594,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Byn, Hjd</t>
+          <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>470959</v>
+        <v>471001</v>
       </c>
       <c r="R38" t="n">
-        <v>6878688</v>
+        <v>6878779</v>
       </c>
       <c r="S38" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4812,22 +4648,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4842,27 +4668,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119852187</v>
+        <v>119483742</v>
       </c>
       <c r="B39" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4870,48 +4691,46 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>471061</v>
+        <v>471010</v>
       </c>
       <c r="R39" t="n">
-        <v>6878956</v>
+        <v>6878760</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4935,22 +4754,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:59</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:59</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4965,27 +4774,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119851909</v>
+        <v>119483868</v>
       </c>
       <c r="B40" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4993,44 +4797,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>470853</v>
+        <v>470973</v>
       </c>
       <c r="R40" t="n">
-        <v>6878846</v>
+        <v>6878820</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5054,22 +4851,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:37</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:37</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5084,31 +4871,26 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119852001</v>
+        <v>119484128</v>
       </c>
       <c r="B41" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -5129,31 +4911,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>470930</v>
+        <v>471106</v>
       </c>
       <c r="R41" t="n">
-        <v>6878867</v>
+        <v>6878960</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5177,22 +4948,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:44</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:44</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5207,76 +4968,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119851504</v>
+        <v>119484672</v>
       </c>
       <c r="B42" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>470768</v>
+        <v>471128</v>
       </c>
       <c r="R42" t="n">
-        <v>6878900</v>
+        <v>6878894</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5300,22 +5045,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5330,27 +5065,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119851125</v>
+        <v>119484855</v>
       </c>
       <c r="B43" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5358,41 +5088,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Byn, Hjd</t>
+          <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>470895</v>
+        <v>471057</v>
       </c>
       <c r="R43" t="n">
-        <v>6878676</v>
+        <v>6878837</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5419,22 +5142,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5449,27 +5162,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119852400</v>
+        <v>119722321</v>
       </c>
       <c r="B44" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5477,24 +5185,28 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -5508,13 +5220,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471011</v>
+        <v>471031</v>
       </c>
       <c r="R44" t="n">
-        <v>6878716</v>
+        <v>6878684</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5538,22 +5250,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5580,42 +5292,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119851603</v>
+        <v>119723116</v>
       </c>
       <c r="B45" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5627,17 +5334,17 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Håtjärnen, Hjd</t>
+          <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>470770</v>
+        <v>471051</v>
       </c>
       <c r="R45" t="n">
-        <v>6878837</v>
+        <v>6878742</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5661,22 +5368,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5703,15 +5410,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119851206</v>
+        <v>119724435</v>
       </c>
       <c r="B46" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5719,26 +5421,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5750,14 +5452,14 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Byn, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>470886</v>
+        <v>471045</v>
       </c>
       <c r="R46" t="n">
-        <v>6878669</v>
+        <v>6878839</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5784,22 +5486,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5826,40 +5528,39 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119850928</v>
+        <v>119724502</v>
       </c>
       <c r="B47" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -5869,14 +5570,14 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Byn, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>470974</v>
+        <v>470964</v>
       </c>
       <c r="R47" t="n">
-        <v>6878669</v>
+        <v>6878819</v>
       </c>
       <c r="S47" t="n">
         <v>9</v>
@@ -5903,22 +5604,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5945,19 +5646,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119852261</v>
+        <v>119724643</v>
       </c>
       <c r="B48" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5980,7 +5676,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5996,10 +5692,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>471097</v>
+        <v>470980</v>
       </c>
       <c r="R48" t="n">
-        <v>6878967</v>
+        <v>6878815</v>
       </c>
       <c r="S48" t="n">
         <v>7</v>
@@ -6026,22 +5722,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6068,15 +5764,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119852126</v>
+        <v>119724688</v>
       </c>
       <c r="B49" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6084,26 +5775,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6119,10 +5810,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>471009</v>
+        <v>471003</v>
       </c>
       <c r="R49" t="n">
-        <v>6878908</v>
+        <v>6878824</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -6149,22 +5840,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6191,44 +5882,35 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119851525</v>
+        <v>119851345</v>
       </c>
       <c r="B50" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6238,17 +5920,17 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>470762</v>
+        <v>470849</v>
       </c>
       <c r="R50" t="n">
-        <v>6878911</v>
+        <v>6878651</v>
       </c>
       <c r="S50" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6277,7 +5959,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6287,7 +5969,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6314,15 +5996,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119852292</v>
+        <v>119852001</v>
       </c>
       <c r="B51" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6330,24 +6007,28 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6361,13 +6042,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>471113</v>
+        <v>470930</v>
       </c>
       <c r="R51" t="n">
-        <v>6878966</v>
+        <v>6878867</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6396,7 +6077,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6406,7 +6087,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6433,19 +6114,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119851345</v>
+        <v>119852069</v>
       </c>
       <c r="B52" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -6466,7 +6142,11 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6476,17 +6156,17 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Byn, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>470849</v>
+        <v>470957</v>
       </c>
       <c r="R52" t="n">
-        <v>6878651</v>
+        <v>6878845</v>
       </c>
       <c r="S52" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6515,7 +6195,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6525,7 +6205,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6552,15 +6232,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119852152</v>
+        <v>119852261</v>
       </c>
       <c r="B53" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6568,25 +6243,33 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -6595,10 +6278,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>471012</v>
+        <v>471097</v>
       </c>
       <c r="R53" t="n">
-        <v>6878913</v>
+        <v>6878967</v>
       </c>
       <c r="S53" t="n">
         <v>7</v>
@@ -6630,7 +6313,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6640,7 +6323,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6667,15 +6350,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119851314</v>
+        <v>119724366</v>
       </c>
       <c r="B54" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6683,26 +6361,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6714,17 +6392,17 @@
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Byn, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>470863</v>
+        <v>471081</v>
       </c>
       <c r="R54" t="n">
-        <v>6878623</v>
+        <v>6878832</v>
       </c>
       <c r="S54" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6748,22 +6426,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6790,44 +6468,35 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119852069</v>
+        <v>119850928</v>
       </c>
       <c r="B55" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6837,17 +6506,17 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>470957</v>
+        <v>470974</v>
       </c>
       <c r="R55" t="n">
-        <v>6878845</v>
+        <v>6878669</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6876,7 +6545,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6886,7 +6555,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6910,6 +6579,563 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>119851504</v>
+      </c>
+      <c r="B56" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Vakomansbacken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>470768</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6878900</v>
+      </c>
+      <c r="S56" t="n">
+        <v>6</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Bror Österman</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Bror Österman</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>119851525</v>
+      </c>
+      <c r="B57" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Vakomansbacken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>470762</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6878911</v>
+      </c>
+      <c r="S57" t="n">
+        <v>16</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Bror Österman</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Bror Österman</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>119851603</v>
+      </c>
+      <c r="B58" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Håtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>470770</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6878837</v>
+      </c>
+      <c r="S58" t="n">
+        <v>7</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Bror Österman</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Bror Österman</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>119485062</v>
+      </c>
+      <c r="B59" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Byn, Byn, Hjd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>471107</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6878831</v>
+      </c>
+      <c r="S59" t="n">
+        <v>20</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>119484595</v>
+      </c>
+      <c r="B60" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Byn, Byn, Hjd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>471134</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6878944</v>
+      </c>
+      <c r="S60" t="n">
+        <v>20</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63663-2025 artfynd.xlsx
+++ b/artfynd/A 63663-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AZ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112056771</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112056821</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112106065</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483639</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483766</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,6 +1322,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119722350</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119722627</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119723069</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1642,6 +1687,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851125</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1760,6 +1810,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851206</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1874,6 +1929,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851909</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1988,6 +2048,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119852400</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2086,6 +2151,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112056968</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2184,6 +2254,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112057042</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2282,6 +2357,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112105915</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2380,6 +2460,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112106066</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2478,6 +2563,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112106172</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2584,6 +2674,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483537</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2690,6 +2785,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483707</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2796,6 +2896,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483785</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2902,6 +3007,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483848</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3008,6 +3118,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483937</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3114,6 +3229,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483969</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3220,6 +3340,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119484119</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3326,6 +3451,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119484702</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3432,6 +3562,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119484942</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3550,6 +3685,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119722408</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3668,6 +3808,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119722501</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3786,6 +3931,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119722838</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3904,6 +4054,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119722968</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4022,6 +4177,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851314</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4140,6 +4300,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119852126</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4250,6 +4415,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119852152</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4368,6 +4538,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119852187</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4482,6 +4657,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119852292</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4580,6 +4760,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112056985</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4677,6 +4862,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483661</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4783,6 +4973,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483742</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4880,6 +5075,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483868</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4977,6 +5177,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119484128</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5074,6 +5279,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119484672</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5171,6 +5381,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119484855</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5289,6 +5504,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119722321</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5407,6 +5627,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119723116</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5525,6 +5750,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119724435</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5643,6 +5873,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119724502</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5761,6 +5996,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119724643</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5879,6 +6119,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119724688</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5993,6 +6238,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851345</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6111,6 +6361,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119852001</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6229,6 +6484,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119852069</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6347,6 +6607,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119852261</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6465,6 +6730,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119724366</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6579,6 +6849,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850928</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6697,6 +6972,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851504</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6815,6 +7095,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851525</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6933,6 +7218,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851603</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7030,6 +7320,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119485062</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7136,8 +7431,74 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119484595</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 63663-2025 artfynd.xlsx
+++ b/artfynd/A 63663-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ60"/>
+  <dimension ref="A1:AZ74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,46 +680,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112056771</v>
+        <v>136382139</v>
       </c>
       <c r="B2" t="n">
-        <v>93189</v>
+        <v>93401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Byn, Hjd</t>
+          <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471058</v>
+        <v>470820</v>
       </c>
       <c r="R2" t="n">
-        <v>6878706</v>
+        <v>6878870</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -746,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,13 +785,13 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112056771</t>
+          <t>https://artportalen.se/Sighting/136382139</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112056821</v>
+        <v>112056771</v>
       </c>
       <c r="B3" t="n">
         <v>93189</v>
@@ -819,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471005</v>
+        <v>471058</v>
       </c>
       <c r="R3" t="n">
-        <v>6878689</v>
+        <v>6878706</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -880,13 +888,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112056821</t>
+          <t>https://artportalen.se/Sighting/112056771</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112106065</v>
+        <v>112056821</v>
       </c>
       <c r="B4" t="n">
         <v>93189</v>
@@ -918,14 +926,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>470881</v>
+        <v>471005</v>
       </c>
       <c r="R4" t="n">
-        <v>6879329</v>
+        <v>6878689</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -952,12 +960,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,13 +991,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112106065</t>
+          <t>https://artportalen.se/Sighting/112056821</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119483639</v>
+        <v>112106065</v>
       </c>
       <c r="B5" t="n">
         <v>93189</v>
@@ -1017,26 +1025,18 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Byn, Byn, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471001</v>
+        <v>470881</v>
       </c>
       <c r="R5" t="n">
-        <v>6878779</v>
+        <v>6879329</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,13 +1094,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119483639</t>
+          <t>https://artportalen.se/Sighting/112106065</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119483766</v>
+        <v>119483639</v>
       </c>
       <c r="B6" t="n">
         <v>93189</v>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471006</v>
+        <v>471001</v>
       </c>
       <c r="R6" t="n">
-        <v>6878778</v>
+        <v>6878779</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1205,13 +1205,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119483766</t>
+          <t>https://artportalen.se/Sighting/119483639</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119722350</v>
+        <v>119483766</v>
       </c>
       <c r="B7" t="n">
         <v>93189</v>
@@ -1244,22 +1244,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Byn, Hjd</t>
+          <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471026</v>
+        <v>471006</v>
       </c>
       <c r="R7" t="n">
-        <v>6878688</v>
+        <v>6878778</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,22 +1285,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:05</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:05</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,24 +1305,24 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119722350</t>
+          <t>https://artportalen.se/Sighting/119483766</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119722627</v>
+        <v>119722350</v>
       </c>
       <c r="B8" t="n">
         <v>93189</v>
@@ -1360,14 +1352,10 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1376,13 +1364,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470974</v>
+        <v>471026</v>
       </c>
       <c r="R8" t="n">
-        <v>6878769</v>
+        <v>6878688</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1411,7 +1399,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1409,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,13 +1435,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119722627</t>
+          <t>https://artportalen.se/Sighting/119722350</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119723069</v>
+        <v>119722627</v>
       </c>
       <c r="B9" t="n">
         <v>93189</v>
@@ -1483,7 +1471,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1499,13 +1487,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471053</v>
+        <v>470974</v>
       </c>
       <c r="R9" t="n">
-        <v>6878751</v>
+        <v>6878769</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1522,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1532,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,13 +1558,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119723069</t>
+          <t>https://artportalen.se/Sighting/119722627</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119851125</v>
+        <v>119723069</v>
       </c>
       <c r="B10" t="n">
         <v>93189</v>
@@ -1604,7 +1592,11 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1618,13 +1610,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>470895</v>
+        <v>471053</v>
       </c>
       <c r="R10" t="n">
-        <v>6878676</v>
+        <v>6878751</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1648,22 +1640,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,13 +1681,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119851125</t>
+          <t>https://artportalen.se/Sighting/119723069</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119851206</v>
+        <v>119851125</v>
       </c>
       <c r="B11" t="n">
         <v>93189</v>
@@ -1723,11 +1715,7 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1741,13 +1729,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470886</v>
+        <v>470895</v>
       </c>
       <c r="R11" t="n">
-        <v>6878669</v>
+        <v>6878676</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1776,7 +1764,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,7 +1774,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,13 +1800,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119851206</t>
+          <t>https://artportalen.se/Sighting/119851125</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119851909</v>
+        <v>119851206</v>
       </c>
       <c r="B12" t="n">
         <v>93189</v>
@@ -1846,7 +1834,11 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1856,17 +1848,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470853</v>
+        <v>470886</v>
       </c>
       <c r="R12" t="n">
-        <v>6878846</v>
+        <v>6878669</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1895,7 +1887,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1897,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,13 +1923,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119851909</t>
+          <t>https://artportalen.se/Sighting/119851206</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119852400</v>
+        <v>119851909</v>
       </c>
       <c r="B13" t="n">
         <v>93189</v>
@@ -1975,17 +1967,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Byn, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471011</v>
+        <v>470853</v>
       </c>
       <c r="R13" t="n">
-        <v>6878716</v>
+        <v>6878846</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2014,7 +2006,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,7 +2016,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,16 +2042,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119852400</t>
+          <t>https://artportalen.se/Sighting/119851909</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112056968</v>
+        <v>119852400</v>
       </c>
       <c r="B14" t="n">
-        <v>93191</v>
+        <v>93189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,38 +2059,44 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471057</v>
+        <v>471011</v>
       </c>
       <c r="R14" t="n">
-        <v>6878932</v>
+        <v>6878716</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2122,12 +2120,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2142,27 +2150,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112056968</t>
+          <t>https://artportalen.se/Sighting/119852400</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112057042</v>
+        <v>136379574</v>
       </c>
       <c r="B15" t="n">
-        <v>93191</v>
+        <v>93377</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,35 +2178,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Byn, Hjd</t>
+          <t>Vakomansbacken, Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471107</v>
+        <v>470912</v>
       </c>
       <c r="R15" t="n">
-        <v>6878973</v>
+        <v>6879329</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2225,12 +2241,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,16 +2272,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112057042</t>
+          <t>https://artportalen.se/Sighting/136379574</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112105915</v>
+        <v>136379908</v>
       </c>
       <c r="B16" t="n">
-        <v>93191</v>
+        <v>93377</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,35 +2289,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Vakomansbacken, Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470952</v>
+        <v>470882</v>
       </c>
       <c r="R16" t="n">
-        <v>6879263</v>
+        <v>6879344</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2328,12 +2352,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2359,16 +2383,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112105915</t>
+          <t>https://artportalen.se/Sighting/136379908</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112106066</v>
+        <v>136380663</v>
       </c>
       <c r="B17" t="n">
-        <v>93191</v>
+        <v>93377</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2376,38 +2400,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Vakomansbacken, Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470881</v>
+        <v>470819</v>
       </c>
       <c r="R17" t="n">
-        <v>6879329</v>
+        <v>6879224</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2431,12 +2463,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2462,13 +2494,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112106066</t>
+          <t>https://artportalen.se/Sighting/136380663</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112106172</v>
+        <v>112056968</v>
       </c>
       <c r="B18" t="n">
         <v>93191</v>
@@ -2500,14 +2532,14 @@
       <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>470975</v>
+        <v>471057</v>
       </c>
       <c r="R18" t="n">
-        <v>6879312</v>
+        <v>6878932</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2534,12 +2566,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2565,13 +2597,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112106172</t>
+          <t>https://artportalen.se/Sighting/112056968</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119483537</v>
+        <v>112057042</v>
       </c>
       <c r="B19" t="n">
         <v>93191</v>
@@ -2599,26 +2631,18 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Byn, Byn, Hjd</t>
+          <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471054</v>
+        <v>471107</v>
       </c>
       <c r="R19" t="n">
-        <v>6878750</v>
+        <v>6878973</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2645,12 +2669,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2676,13 +2700,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119483537</t>
+          <t>https://artportalen.se/Sighting/112057042</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119483707</v>
+        <v>112105915</v>
       </c>
       <c r="B20" t="n">
         <v>93191</v>
@@ -2710,29 +2734,21 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Byn, Byn, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471012</v>
+        <v>470952</v>
       </c>
       <c r="R20" t="n">
-        <v>6878782</v>
+        <v>6879263</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2756,12 +2772,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2787,13 +2803,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119483707</t>
+          <t>https://artportalen.se/Sighting/112105915</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119483785</v>
+        <v>112106066</v>
       </c>
       <c r="B21" t="n">
         <v>93191</v>
@@ -2821,26 +2837,18 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Byn, Byn, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>470997</v>
+        <v>470881</v>
       </c>
       <c r="R21" t="n">
-        <v>6878764</v>
+        <v>6879329</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2867,12 +2875,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2898,13 +2906,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119483785</t>
+          <t>https://artportalen.se/Sighting/112106066</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119483848</v>
+        <v>112106172</v>
       </c>
       <c r="B22" t="n">
         <v>93191</v>
@@ -2932,26 +2940,18 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Byn, Byn, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>470976</v>
+        <v>470975</v>
       </c>
       <c r="R22" t="n">
-        <v>6878820</v>
+        <v>6879312</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2978,12 +2978,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3009,13 +3009,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119483848</t>
+          <t>https://artportalen.se/Sighting/112106172</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119483937</v>
+        <v>119483537</v>
       </c>
       <c r="B23" t="n">
         <v>93191</v>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>470993</v>
+        <v>471054</v>
       </c>
       <c r="R23" t="n">
-        <v>6878920</v>
+        <v>6878750</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3120,13 +3120,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119483937</t>
+          <t>https://artportalen.se/Sighting/119483537</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119483969</v>
+        <v>119483707</v>
       </c>
       <c r="B24" t="n">
         <v>93191</v>
@@ -3170,13 +3170,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>471041</v>
+        <v>471012</v>
       </c>
       <c r="R24" t="n">
-        <v>6878936</v>
+        <v>6878782</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3231,13 +3231,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119483969</t>
+          <t>https://artportalen.se/Sighting/119483707</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119484119</v>
+        <v>119483785</v>
       </c>
       <c r="B25" t="n">
         <v>93191</v>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>471106</v>
+        <v>470997</v>
       </c>
       <c r="R25" t="n">
-        <v>6878960</v>
+        <v>6878764</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3342,13 +3342,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119484119</t>
+          <t>https://artportalen.se/Sighting/119483785</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119484702</v>
+        <v>119483848</v>
       </c>
       <c r="B26" t="n">
         <v>93191</v>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>471098</v>
+        <v>470976</v>
       </c>
       <c r="R26" t="n">
-        <v>6878877</v>
+        <v>6878820</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3453,13 +3453,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119484702</t>
+          <t>https://artportalen.se/Sighting/119483848</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119484942</v>
+        <v>119483937</v>
       </c>
       <c r="B27" t="n">
         <v>93191</v>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471057</v>
+        <v>470993</v>
       </c>
       <c r="R27" t="n">
-        <v>6878837</v>
+        <v>6878920</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3564,13 +3564,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119484942</t>
+          <t>https://artportalen.se/Sighting/119483937</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119722408</v>
+        <v>119483969</v>
       </c>
       <c r="B28" t="n">
         <v>93191</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3608,21 +3608,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Byn, Hjd</t>
+          <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>470980</v>
+        <v>471041</v>
       </c>
       <c r="R28" t="n">
-        <v>6878652</v>
+        <v>6878936</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3646,22 +3644,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:10</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:10</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3676,24 +3664,24 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119722408</t>
+          <t>https://artportalen.se/Sighting/119483969</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119722501</v>
+        <v>119484119</v>
       </c>
       <c r="B29" t="n">
         <v>93191</v>
@@ -3728,24 +3716,22 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Byn, Hjd</t>
+          <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>470963</v>
+        <v>471106</v>
       </c>
       <c r="R29" t="n">
-        <v>6878709</v>
+        <v>6878960</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3769,22 +3755,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:16</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:16</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3799,24 +3775,24 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119722501</t>
+          <t>https://artportalen.se/Sighting/119484119</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119722838</v>
+        <v>119484702</v>
       </c>
       <c r="B30" t="n">
         <v>93191</v>
@@ -3854,21 +3830,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471024</v>
+        <v>471098</v>
       </c>
       <c r="R30" t="n">
-        <v>6878826</v>
+        <v>6878877</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3892,22 +3866,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3922,24 +3886,24 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119722838</t>
+          <t>https://artportalen.se/Sighting/119484702</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119722968</v>
+        <v>119484942</v>
       </c>
       <c r="B31" t="n">
         <v>93191</v>
@@ -3969,29 +3933,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Byn, Hjd</t>
+          <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>471042</v>
+        <v>471057</v>
       </c>
       <c r="R31" t="n">
-        <v>6878767</v>
+        <v>6878837</v>
       </c>
       <c r="S31" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4015,22 +3977,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4045,24 +3997,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119722968</t>
+          <t>https://artportalen.se/Sighting/119484942</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119851314</v>
+        <v>119722408</v>
       </c>
       <c r="B32" t="n">
         <v>93191</v>
@@ -4108,10 +4060,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>470863</v>
+        <v>470980</v>
       </c>
       <c r="R32" t="n">
-        <v>6878623</v>
+        <v>6878652</v>
       </c>
       <c r="S32" t="n">
         <v>6</v>
@@ -4138,22 +4090,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4179,13 +4131,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119851314</t>
+          <t>https://artportalen.se/Sighting/119722408</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119852126</v>
+        <v>119722501</v>
       </c>
       <c r="B33" t="n">
         <v>93191</v>
@@ -4215,7 +4167,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4227,17 +4179,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>471009</v>
+        <v>470963</v>
       </c>
       <c r="R33" t="n">
-        <v>6878908</v>
+        <v>6878709</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4261,22 +4213,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4302,13 +4254,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119852126</t>
+          <t>https://artportalen.se/Sighting/119722501</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119852152</v>
+        <v>119722838</v>
       </c>
       <c r="B34" t="n">
         <v>93191</v>
@@ -4336,8 +4288,16 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -4346,10 +4306,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>471012</v>
+        <v>471024</v>
       </c>
       <c r="R34" t="n">
-        <v>6878913</v>
+        <v>6878826</v>
       </c>
       <c r="S34" t="n">
         <v>7</v>
@@ -4376,22 +4336,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4417,13 +4377,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119852152</t>
+          <t>https://artportalen.se/Sighting/119722838</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119852187</v>
+        <v>119722968</v>
       </c>
       <c r="B35" t="n">
         <v>93191</v>
@@ -4453,7 +4413,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4465,17 +4425,17 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471061</v>
+        <v>471042</v>
       </c>
       <c r="R35" t="n">
-        <v>6878956</v>
+        <v>6878767</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4499,22 +4459,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4540,13 +4500,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119852187</t>
+          <t>https://artportalen.se/Sighting/119722968</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119852292</v>
+        <v>119851314</v>
       </c>
       <c r="B36" t="n">
         <v>93191</v>
@@ -4574,7 +4534,11 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -4584,17 +4548,17 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>471113</v>
+        <v>470863</v>
       </c>
       <c r="R36" t="n">
-        <v>6878966</v>
+        <v>6878623</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4623,7 +4587,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4633,7 +4597,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4659,16 +4623,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119852292</t>
+          <t>https://artportalen.se/Sighting/119851314</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112056985</v>
+        <v>119852126</v>
       </c>
       <c r="B37" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4676,38 +4640,48 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Byn, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>471107</v>
+        <v>471009</v>
       </c>
       <c r="R37" t="n">
-        <v>6878973</v>
+        <v>6878908</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4731,12 +4705,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4751,27 +4735,27 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112056985</t>
+          <t>https://artportalen.se/Sighting/119852126</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119483661</v>
+        <v>119852152</v>
       </c>
       <c r="B38" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4779,37 +4763,40 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Byn, Byn, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>471001</v>
+        <v>471012</v>
       </c>
       <c r="R38" t="n">
-        <v>6878779</v>
+        <v>6878913</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4833,12 +4820,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4853,27 +4850,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119483661</t>
+          <t>https://artportalen.se/Sighting/119852152</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119483742</v>
+        <v>119852187</v>
       </c>
       <c r="B39" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4881,46 +4878,48 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Byn, Byn, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>471010</v>
+        <v>471061</v>
       </c>
       <c r="R39" t="n">
-        <v>6878760</v>
+        <v>6878956</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4944,12 +4943,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4964,27 +4973,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119483742</t>
+          <t>https://artportalen.se/Sighting/119852187</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119483868</v>
+        <v>119852292</v>
       </c>
       <c r="B40" t="n">
-        <v>93197</v>
+        <v>93191</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4992,37 +5001,44 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Byn, Byn, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>470973</v>
+        <v>471113</v>
       </c>
       <c r="R40" t="n">
-        <v>6878820</v>
+        <v>6878966</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5046,12 +5062,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5066,27 +5092,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119483868</t>
+          <t>https://artportalen.se/Sighting/119852292</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119484128</v>
+        <v>136379397</v>
       </c>
       <c r="B41" t="n">
-        <v>93197</v>
+        <v>93379</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5094,34 +5120,43 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Byn, Byn, Hjd</t>
+          <t>Vakomansbacken, Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>471106</v>
+        <v>470985</v>
       </c>
       <c r="R41" t="n">
-        <v>6878960</v>
+        <v>6879327</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5148,12 +5183,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5179,16 +5214,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119484128</t>
+          <t>https://artportalen.se/Sighting/136379397</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119484672</v>
+        <v>136379836</v>
       </c>
       <c r="B42" t="n">
-        <v>93197</v>
+        <v>93379</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5196,34 +5231,43 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Byn, Byn, Hjd</t>
+          <t>Vakomansbacken, Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>471128</v>
+        <v>470868</v>
       </c>
       <c r="R42" t="n">
-        <v>6878894</v>
+        <v>6879342</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5250,12 +5294,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5281,13 +5325,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119484672</t>
+          <t>https://artportalen.se/Sighting/136379836</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119484855</v>
+        <v>112056985</v>
       </c>
       <c r="B43" t="n">
         <v>93197</v>
@@ -5316,16 +5360,17 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Byn, Byn, Hjd</t>
+          <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>471057</v>
+        <v>471107</v>
       </c>
       <c r="R43" t="n">
-        <v>6878837</v>
+        <v>6878973</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5352,12 +5397,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5383,13 +5428,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119484855</t>
+          <t>https://artportalen.se/Sighting/112056985</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119722321</v>
+        <v>119483661</v>
       </c>
       <c r="B44" t="n">
         <v>93197</v>
@@ -5417,31 +5462,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Byn, Hjd</t>
+          <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>471031</v>
+        <v>471001</v>
       </c>
       <c r="R44" t="n">
-        <v>6878684</v>
+        <v>6878779</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5465,22 +5499,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5495,24 +5519,24 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119722321</t>
+          <t>https://artportalen.se/Sighting/119483661</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119723116</v>
+        <v>119483742</v>
       </c>
       <c r="B45" t="n">
         <v>93197</v>
@@ -5547,24 +5571,22 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Byn, Hjd</t>
+          <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>471051</v>
+        <v>471010</v>
       </c>
       <c r="R45" t="n">
-        <v>6878742</v>
+        <v>6878760</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5588,22 +5610,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5618,24 +5630,24 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119723116</t>
+          <t>https://artportalen.se/Sighting/119483742</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119724435</v>
+        <v>119483868</v>
       </c>
       <c r="B46" t="n">
         <v>93197</v>
@@ -5663,31 +5675,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>471045</v>
+        <v>470973</v>
       </c>
       <c r="R46" t="n">
-        <v>6878839</v>
+        <v>6878820</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5711,22 +5712,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5741,24 +5732,24 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119724435</t>
+          <t>https://artportalen.se/Sighting/119483868</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119724502</v>
+        <v>119484128</v>
       </c>
       <c r="B47" t="n">
         <v>93197</v>
@@ -5786,31 +5777,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>470964</v>
+        <v>471106</v>
       </c>
       <c r="R47" t="n">
-        <v>6878819</v>
+        <v>6878960</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5834,22 +5814,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5864,24 +5834,24 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119724502</t>
+          <t>https://artportalen.se/Sighting/119484128</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119724643</v>
+        <v>119484672</v>
       </c>
       <c r="B48" t="n">
         <v>93197</v>
@@ -5909,31 +5879,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>470980</v>
+        <v>471128</v>
       </c>
       <c r="R48" t="n">
-        <v>6878815</v>
+        <v>6878894</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5957,22 +5916,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>15:52</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>15:52</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5987,24 +5936,24 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119724643</t>
+          <t>https://artportalen.se/Sighting/119484672</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119724688</v>
+        <v>119484855</v>
       </c>
       <c r="B49" t="n">
         <v>93197</v>
@@ -6032,31 +5981,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Byn, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>471003</v>
+        <v>471057</v>
       </c>
       <c r="R49" t="n">
-        <v>6878824</v>
+        <v>6878837</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6080,22 +6018,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:55</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:55</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6110,24 +6038,24 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bror Österman</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119724688</t>
+          <t>https://artportalen.se/Sighting/119484855</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119851345</v>
+        <v>119722321</v>
       </c>
       <c r="B50" t="n">
         <v>93197</v>
@@ -6155,7 +6083,11 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6169,13 +6101,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>470849</v>
+        <v>471031</v>
       </c>
       <c r="R50" t="n">
-        <v>6878651</v>
+        <v>6878684</v>
       </c>
       <c r="S50" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6199,22 +6131,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6240,13 +6172,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119851345</t>
+          <t>https://artportalen.se/Sighting/119722321</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119852001</v>
+        <v>119723116</v>
       </c>
       <c r="B51" t="n">
         <v>93197</v>
@@ -6276,7 +6208,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6288,14 +6220,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>470930</v>
+        <v>471051</v>
       </c>
       <c r="R51" t="n">
-        <v>6878867</v>
+        <v>6878742</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6322,22 +6254,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6363,13 +6295,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119852001</t>
+          <t>https://artportalen.se/Sighting/119723116</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119852069</v>
+        <v>119724435</v>
       </c>
       <c r="B52" t="n">
         <v>93197</v>
@@ -6399,7 +6331,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6415,13 +6347,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>470957</v>
+        <v>471045</v>
       </c>
       <c r="R52" t="n">
-        <v>6878845</v>
+        <v>6878839</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6445,22 +6377,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6486,13 +6418,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119852069</t>
+          <t>https://artportalen.se/Sighting/119724435</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119852261</v>
+        <v>119724502</v>
       </c>
       <c r="B53" t="n">
         <v>93197</v>
@@ -6522,7 +6454,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6538,13 +6470,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>471097</v>
+        <v>470964</v>
       </c>
       <c r="R53" t="n">
-        <v>6878967</v>
+        <v>6878819</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6568,22 +6500,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6609,16 +6541,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119852261</t>
+          <t>https://artportalen.se/Sighting/119724502</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119724366</v>
+        <v>119724643</v>
       </c>
       <c r="B54" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6626,21 +6558,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6661,13 +6593,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>471081</v>
+        <v>470980</v>
       </c>
       <c r="R54" t="n">
-        <v>6878832</v>
+        <v>6878815</v>
       </c>
       <c r="S54" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6696,7 +6628,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6706,7 +6638,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6732,16 +6664,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119724366</t>
+          <t>https://artportalen.se/Sighting/119724643</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119850928</v>
+        <v>119724688</v>
       </c>
       <c r="B55" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6749,24 +6681,28 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6776,14 +6712,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Byn, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>470974</v>
+        <v>471003</v>
       </c>
       <c r="R55" t="n">
-        <v>6878669</v>
+        <v>6878824</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -6810,22 +6746,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6851,16 +6787,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119850928</t>
+          <t>https://artportalen.se/Sighting/119724688</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119851504</v>
+        <v>119851345</v>
       </c>
       <c r="B56" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6868,28 +6804,24 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6899,17 +6831,17 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vakomansbacken, Hjd</t>
+          <t>Byn, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>470768</v>
+        <v>470849</v>
       </c>
       <c r="R56" t="n">
-        <v>6878900</v>
+        <v>6878651</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6938,7 +6870,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6948,7 +6880,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6974,16 +6906,16 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119851504</t>
+          <t>https://artportalen.se/Sighting/119851345</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119851525</v>
+        <v>119852001</v>
       </c>
       <c r="B57" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6991,26 +6923,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7026,13 +6958,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>470762</v>
+        <v>470930</v>
       </c>
       <c r="R57" t="n">
-        <v>6878911</v>
+        <v>6878867</v>
       </c>
       <c r="S57" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7061,7 +6993,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7071,7 +7003,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7097,16 +7029,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119851525</t>
+          <t>https://artportalen.se/Sighting/119852001</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119851603</v>
+        <v>119852069</v>
       </c>
       <c r="B58" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7114,26 +7046,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7145,17 +7077,17 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Håtjärnen, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>470770</v>
+        <v>470957</v>
       </c>
       <c r="R58" t="n">
-        <v>6878837</v>
+        <v>6878845</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7184,7 +7116,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7194,7 +7126,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7220,16 +7152,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119851603</t>
+          <t>https://artportalen.se/Sighting/119852069</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119485062</v>
+        <v>119852261</v>
       </c>
       <c r="B59" t="n">
-        <v>92841</v>
+        <v>93197</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7237,37 +7169,48 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Byn, Byn, Hjd</t>
+          <t>Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>471107</v>
+        <v>471097</v>
       </c>
       <c r="R59" t="n">
-        <v>6878831</v>
+        <v>6878967</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7291,12 +7234,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7311,54 +7264,54 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bror Österman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119485062</t>
+          <t>https://artportalen.se/Sighting/119852261</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119484595</v>
+        <v>136379494</v>
       </c>
       <c r="B60" t="n">
-        <v>90691</v>
+        <v>93385</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7368,14 +7321,14 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Byn, Byn, Hjd</t>
+          <t>Vakomansbacken, Vakomansbacken, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>471134</v>
+        <v>470962</v>
       </c>
       <c r="R60" t="n">
-        <v>6878944</v>
+        <v>6879322</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7402,12 +7355,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7432,6 +7385,1607 @@
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136379494</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>136379725</v>
+      </c>
+      <c r="B61" t="n">
+        <v>93385</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Vakomansbacken, Vakomansbacken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>470881</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6879339</v>
+      </c>
+      <c r="S61" t="n">
+        <v>20</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136379725</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>136380175</v>
+      </c>
+      <c r="B62" t="n">
+        <v>93385</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Vakomansbacken, Vakomansbacken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>470725</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6879110</v>
+      </c>
+      <c r="S62" t="n">
+        <v>20</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136380175</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>136380321</v>
+      </c>
+      <c r="B63" t="n">
+        <v>93385</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Vakomansbacken, Vakomansbacken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>470760</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6879127</v>
+      </c>
+      <c r="S63" t="n">
+        <v>20</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136380321</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>136380437</v>
+      </c>
+      <c r="B64" t="n">
+        <v>93385</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Vakomansbacken, Vakomansbacken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>470752</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6879148</v>
+      </c>
+      <c r="S64" t="n">
+        <v>20</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136380437</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>136380929</v>
+      </c>
+      <c r="B65" t="n">
+        <v>93385</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Vakomansbacken, Vakomansbacken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>470934</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6879268</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136380929</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>136380989</v>
+      </c>
+      <c r="B66" t="n">
+        <v>93385</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Vakomansbacken, Vakomansbacken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>470970</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6879313</v>
+      </c>
+      <c r="S66" t="n">
+        <v>20</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136380989</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>119724366</v>
+      </c>
+      <c r="B67" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Vakomansbacken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>471081</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6878832</v>
+      </c>
+      <c r="S67" t="n">
+        <v>14</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Bror Österman</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Bror Österman</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119724366</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>119850928</v>
+      </c>
+      <c r="B68" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Byn, Hjd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>470974</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6878669</v>
+      </c>
+      <c r="S68" t="n">
+        <v>9</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Bror Österman</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Bror Österman</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850928</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>119851504</v>
+      </c>
+      <c r="B69" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Vakomansbacken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>470768</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6878900</v>
+      </c>
+      <c r="S69" t="n">
+        <v>6</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Bror Österman</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Bror Österman</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851504</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>119851525</v>
+      </c>
+      <c r="B70" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Vakomansbacken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>470762</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6878911</v>
+      </c>
+      <c r="S70" t="n">
+        <v>16</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Bror Österman</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Bror Österman</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851525</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>119851603</v>
+      </c>
+      <c r="B71" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Håtjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>470770</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6878837</v>
+      </c>
+      <c r="S71" t="n">
+        <v>7</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Bror Österman</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Bror Österman</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851603</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>136379701</v>
+      </c>
+      <c r="B72" t="n">
+        <v>93397</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Vakomansbacken, Vakomansbacken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>470886</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6879334</v>
+      </c>
+      <c r="S72" t="n">
+        <v>20</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136379701</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>119485062</v>
+      </c>
+      <c r="B73" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Byn, Byn, Hjd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>471107</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6878831</v>
+      </c>
+      <c r="S73" t="n">
+        <v>20</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119485062</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>119484595</v>
+      </c>
+      <c r="B74" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Byn, Byn, Hjd</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>471134</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6878944</v>
+      </c>
+      <c r="S74" t="n">
+        <v>20</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119484595</t>
         </is>
@@ -7498,6 +9052,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63663-2025 artfynd.xlsx
+++ b/artfynd/A 63663-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136382139</v>
       </c>
       <c r="B2" t="n">
-        <v>93401</v>
+        <v>93402</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>136379574</v>
       </c>
       <c r="B15" t="n">
-        <v>93377</v>
+        <v>93378</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>136379908</v>
       </c>
       <c r="B16" t="n">
-        <v>93377</v>
+        <v>93378</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>136380663</v>
       </c>
       <c r="B17" t="n">
-        <v>93377</v>
+        <v>93378</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>136379397</v>
       </c>
       <c r="B41" t="n">
-        <v>93379</v>
+        <v>93380</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>136379836</v>
       </c>
       <c r="B42" t="n">
-        <v>93379</v>
+        <v>93380</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>136379494</v>
       </c>
       <c r="B60" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>136379725</v>
       </c>
       <c r="B61" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>136380175</v>
       </c>
       <c r="B62" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>136380321</v>
       </c>
       <c r="B63" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>136380437</v>
       </c>
       <c r="B64" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>136380929</v>
       </c>
       <c r="B65" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>136380989</v>
       </c>
       <c r="B66" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>136379701</v>
       </c>
       <c r="B72" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 63663-2025 artfynd.xlsx
+++ b/artfynd/A 63663-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136382139</v>
       </c>
       <c r="B2" t="n">
-        <v>93402</v>
+        <v>93415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>136379574</v>
       </c>
       <c r="B15" t="n">
-        <v>93378</v>
+        <v>93391</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>136379908</v>
       </c>
       <c r="B16" t="n">
-        <v>93378</v>
+        <v>93391</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>136380663</v>
       </c>
       <c r="B17" t="n">
-        <v>93378</v>
+        <v>93391</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>136379397</v>
       </c>
       <c r="B41" t="n">
-        <v>93380</v>
+        <v>93393</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>136379836</v>
       </c>
       <c r="B42" t="n">
-        <v>93380</v>
+        <v>93393</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>136379494</v>
       </c>
       <c r="B60" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>136379725</v>
       </c>
       <c r="B61" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>136380175</v>
       </c>
       <c r="B62" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>136380321</v>
       </c>
       <c r="B63" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>136380437</v>
       </c>
       <c r="B64" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>136380929</v>
       </c>
       <c r="B65" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>136380989</v>
       </c>
       <c r="B66" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>136379701</v>
       </c>
       <c r="B72" t="n">
-        <v>93398</v>
+        <v>93411</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 63663-2025 artfynd.xlsx
+++ b/artfynd/A 63663-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136382139</v>
       </c>
       <c r="B2" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>136379574</v>
       </c>
       <c r="B15" t="n">
-        <v>93391</v>
+        <v>93392</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>136379908</v>
       </c>
       <c r="B16" t="n">
-        <v>93391</v>
+        <v>93392</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>136380663</v>
       </c>
       <c r="B17" t="n">
-        <v>93391</v>
+        <v>93392</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>136379397</v>
       </c>
       <c r="B41" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>136379836</v>
       </c>
       <c r="B42" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>136379494</v>
       </c>
       <c r="B60" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>136379725</v>
       </c>
       <c r="B61" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>136380175</v>
       </c>
       <c r="B62" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>136380321</v>
       </c>
       <c r="B63" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>136380437</v>
       </c>
       <c r="B64" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>136380929</v>
       </c>
       <c r="B65" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>136380989</v>
       </c>
       <c r="B66" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>136379701</v>
       </c>
       <c r="B72" t="n">
-        <v>93411</v>
+        <v>93412</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
